--- a/data/demoTest.xlsx
+++ b/data/demoTest.xlsx
@@ -862,7 +862,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>23</v>

--- a/data/demoTest.xlsx
+++ b/data/demoTest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -227,7 +227,7 @@
     <xf fontId="0" fillId="5" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -862,9 +862,9 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
-        <v>2026</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -907,7 +907,7 @@
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="4"/>
@@ -962,6 +962,9 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
@@ -1050,22 +1053,25 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/data/demoTest.xlsx
+++ b/data/demoTest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>ACTION</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>softAssertions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$a = 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">echo $a</t>
   </si>
 </sst>
 </file>
@@ -862,9 +868,9 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4">
-        <v>2028</v>
-      </c>
-      <c r="F8" s="5" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -907,7 +913,7 @@
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="4"/>
@@ -1061,16 +1067,26 @@
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>22</v>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>2026</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>23</v>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
